--- a/docs/запуск.xlsx
+++ b/docs/запуск.xlsx
@@ -167,7 +167,7 @@
     <t xml:space="preserve">Отсканировать пробную этикетку, чтобы убрать её со склада</t>
   </si>
   <si>
-    <t xml:space="preserve">Убрать лишние</t>
+    <t xml:space="preserve">Лишние этикетки</t>
   </si>
   <si>
     <t xml:space="preserve">Зелёный экран</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">Утром напечатать этикетки по каждому сборщику и положить в коробку с комплектующими</t>
   </si>
   <si>
-    <t xml:space="preserve">Печать по задачам → «Сегодня» → «Печать для …»</t>
+    <t xml:space="preserve">Печать этикеток → «Сегодня» → «Напечатать всё: …»</t>
   </si>
   <si>
     <t xml:space="preserve">У сборщика «этикеток на руках» = план</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">Отсканировать вернувшиеся зеркала. Без этикетки: напечатать ШК. Всё встаёт на Коминтерна</t>
   </si>
   <si>
-    <t xml:space="preserve">Возвраты; Печать ШК</t>
+    <t xml:space="preserve">Возвраты; Этикетки без ШК</t>
   </si>
   <si>
     <t xml:space="preserve">3.10</t>
@@ -407,10 +407,10 @@
     <t xml:space="preserve">3.12</t>
   </si>
   <si>
-    <t xml:space="preserve">Убрать висящие этикетки по несделанным задачам и скопировать остаток на завтра</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Печать по задачам → «Убрать висящие»; Задачи</t>
+    <t xml:space="preserve">Убрать несданные этикетки по несделанным задачам и скопировать остаток на завтра</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Печать этикеток → «Убрать несданные»; Задачи</t>
   </si>
   <si>
     <t xml:space="preserve">Висящих 0, задачи на завтра стоят</t>

--- a/docs/запуск.xlsx
+++ b/docs/запуск.xlsx
@@ -359,7 +359,7 @@
     <t xml:space="preserve">3.8</t>
   </si>
   <si>
-    <t xml:space="preserve">Выбрать канал (Ozon, WB, СГТ, КГТ, СДЭК), отсканировать зеркала, закрыть канал. Для Ozon выбрать машину Озон1/2/3</t>
+    <t xml:space="preserve">Выбрать канал (Озон 1, Озон 2, Озон 3, WB, СДЭК, СГТ, КГТ), отсканировать зеркала, закрыть канал. Озон 1, Озон 2, Озон 3 — отдельные каналы, их можно грузить одновременно</t>
   </si>
   <si>
     <t xml:space="preserve">Погрузка</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">3.12</t>
   </si>
   <si>
-    <t xml:space="preserve">Убрать несданные этикетки по несделанным задачам и скопировать остаток на завтра</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Печать этикеток → «Убрать несданные»; Задачи</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Висящих 0, задачи на завтра стоят</t>
+    <t xml:space="preserve">Ненаклеенные этикетки по недоделанным задачам сборщики отдают кладовщице, она их сканирует. На завтра начальник ставит задачи заново</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лишние этикетки; Задачи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Несданных 0, задачи на завтра стоят</t>
   </si>
   <si>
     <t xml:space="preserve">3.13</t>
@@ -1701,7 +1701,7 @@
       <c r="G31" s="7"/>
       <c r="H31" s="6"/>
     </row>
-    <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
         <v>110</v>
       </c>
@@ -1781,12 +1781,12 @@
       <c r="G35" s="7"/>
       <c r="H35" s="6"/>
     </row>
-    <row r="36" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>127</v>
